--- a/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten</t>
+          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 4,78</t>
+          <t>4,11; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,42</t>
+          <t>4,43; 5,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,54</t>
+          <t>4,0; 8,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,38</t>
+          <t>4,93; 9,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,34</t>
+          <t>4,98; 6,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,4</t>
+          <t>4,45; 7,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,13</t>
+          <t>4,67; 7,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,69</t>
+          <t>4,86; 5,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,3</t>
+          <t>4,75; 7,32</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 4,75</t>
+          <t>4,2; 4,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,53</t>
+          <t>4,85; 5,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,47</t>
+          <t>5,35; 6,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,0</t>
+          <t>4,19; 4,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,57</t>
+          <t>4,79; 5,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,66</t>
+          <t>4,82; 5,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 4,79</t>
+          <t>4,3; 4,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,44</t>
+          <t>4,92; 5,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 5,92</t>
+          <t>5,18; 5,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,13</t>
+          <t>4,03; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,09</t>
+          <t>4,91; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 5,99</t>
+          <t>5,04; 6,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,6</t>
+          <t>3,85; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,13</t>
+          <t>4,51; 5,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,06</t>
+          <t>5,24; 6,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 4,72</t>
+          <t>4,07; 4,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,44</t>
+          <t>4,79; 5,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,27</t>
+          <t>5,21; 6,29</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 4,73</t>
+          <t>4,26; 4,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,48</t>
+          <t>4,94; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,12</t>
+          <t>5,32; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 4,98</t>
+          <t>4,32; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,38</t>
+          <t>4,87; 5,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,92</t>
+          <t>5,13; 5,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 4,79</t>
+          <t>4,37; 4,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,34</t>
+          <t>4,96; 5,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 5,85</t>
+          <t>5,31; 5,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 4,78</t>
+          <t>4,09; 4,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,4</t>
+          <t>4,43; 5,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,48</t>
+          <t>4,91; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,32</t>
+          <t>4,94; 6,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,55</t>
+          <t>4,6; 7,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,32</t>
+          <t>4,62; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,69</t>
+          <t>4,84; 5,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,32</t>
+          <t>4,68; 7,29</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 4,73</t>
+          <t>4,2; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,53</t>
+          <t>4,86; 5,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,54</t>
+          <t>5,38; 6,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 4,99</t>
+          <t>4,21; 5,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,51</t>
+          <t>4,84; 5,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,66</t>
+          <t>4,78; 5,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,41</t>
+          <t>4,9; 5,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 5,89</t>
+          <t>5,21; 5,88</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,1</t>
+          <t>4,01; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,02</t>
+          <t>4,89; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,09</t>
+          <t>5,0; 6,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,59</t>
+          <t>3,85; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,13</t>
+          <t>4,52; 5,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,93</t>
+          <t>5,26; 6,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 4,73</t>
+          <t>4,06; 4,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,45</t>
+          <t>4,78; 5,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,29</t>
+          <t>5,26; 6,29</t>
         </is>
       </c>
     </row>
@@ -1007,42 +1007,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 4,75</t>
+          <t>4,23; 4,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,46</t>
+          <t>4,92; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,14</t>
+          <t>5,35; 6,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,02</t>
+          <t>4,3; 5,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,37</t>
+          <t>4,86; 5,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 5,94</t>
+          <t>5,1; 5,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 4,8</t>
+          <t>4,36; 4,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,35</t>
+          <t>4,95; 5,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">

--- a/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,99</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 4,7</t>
+          <t>4,92; 9,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,39</t>
+          <t>4,95; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,05</t>
+          <t>4,44; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,28</t>
+          <t>4,09; 4,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,33</t>
+          <t>4,44; 5,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,4</t>
+          <t>4,0; 8,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,43</t>
+          <t>4,66; 7,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,67</t>
+          <t>4,84; 5,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,29</t>
+          <t>4,69; 7,3</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,17</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,16</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,79</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 4,77</t>
+          <t>4,21; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,56</t>
+          <t>4,79; 5,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,49</t>
+          <t>4,8; 5,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,01</t>
+          <t>4,2; 4,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,54</t>
+          <t>4,82; 5,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,63</t>
+          <t>5,33; 6,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 4,8</t>
+          <t>4,28; 4,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,41</t>
+          <t>4,91; 5,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 5,88</t>
+          <t>5,2; 5,92</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,93</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,37</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,4</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,1</t>
+          <t>3,89; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,07</t>
+          <t>4,5; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,15</t>
+          <t>5,24; 7,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,6</t>
+          <t>4,09; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 5,14</t>
+          <t>4,92; 6,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,91</t>
+          <t>4,99; 5,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 4,75</t>
+          <t>4,11; 4,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,41</t>
+          <t>4,78; 5,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,29</t>
+          <t>5,22; 6,27</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,46</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,18</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,67</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 4,75</t>
+          <t>4,32; 4,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,47</t>
+          <t>4,87; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,08</t>
+          <t>5,1; 5,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,0</t>
+          <t>4,24; 4,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,37</t>
+          <t>4,92; 5,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,95</t>
+          <t>5,32; 6,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 4,81</t>
+          <t>4,37; 4,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,33</t>
+          <t>4,97; 5,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 5,88</t>
+          <t>5,33; 5,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,99</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,93</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,9</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5.987557343919507</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.650011641993952</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.382158271157566</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>4.932540424471115</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.794675086625143</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>5.291464613175375</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>5.259070955412039</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>5.895050552722279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 9,38</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,95; 6,34</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,44; 7,4</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,09; 4,78</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,44; 5,42</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,0; 8,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,66; 7,13</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4,84; 5,69</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4,69; 7,3</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>4.918316093582385</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>4.950642723191852</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4.441664724657637</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.094519990623525</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.4432459560515</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.662855106116306</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4.838961426486152</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4.688183957185955</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.384513223990888</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.33887336833438</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.403371705063986</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.775807943068775</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5.423272094188173</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.539400341340817</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>7.132137069203563</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5.69364791920754</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>7.304264577858223</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,53</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,21; 5,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,79; 5,57</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,8; 5,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,2; 4,75</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,82; 5,53</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,33; 6,47</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,28; 4,79</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4,91; 5,44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,2; 5,92</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.586913111347996</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.124946281887725</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.168355141526834</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.457480267689371</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.158165682378701</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.794861719020707</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4.527279087599458</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.141337116534211</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.488038342226304</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.209475882448124</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.790560799597395</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4.799197981434446</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.197718871307107</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.815636153973555</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>5.331834107757453</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.277463292228742</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4.906884233540957</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.2006010988923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,89; 4,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,5; 5,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,24; 7,06</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4,09; 5,13</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 6,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,99; 5,99</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,11; 4,72</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 5,44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5,22; 6,27</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.997816746454986</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.567499329510862</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.660374416512425</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.746861259961233</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.533156091565989</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6.466346895997852</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.785895041017532</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.43863390049244</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.915091726770633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.203118283917789</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.820537865102162</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.932784483988419</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.569755250987948</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.365652055726269</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5.395566748847007</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>4.387947858896902</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>5.064065775061772</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.674970749150358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,32; 4,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 5,38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 5,92</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 4,73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 5,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,32; 6,12</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,37; 4,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 5,34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,33; 5,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3.892052069402195</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4.496211485285953</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.24371736573278</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4.089505640899594</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4.92036488426277</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4.991013453264825</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.113187111584451</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>4.784392252220917</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.220172512914981</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.598671802764558</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.132429440138432</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.05713688610291</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.128334084549151</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.093933379453097</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.993806835376633</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>4.721632561244928</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5.442262561997522</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.266588296233477</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4.619824165836527</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.084919452672568</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.45947786977918</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.488866288940865</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5.183113466281289</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.668700994366628</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>4.558027774905787</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>5.132672542083224</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5.56415128719219</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4.320594721101513</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4.868761565682787</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.100970737069201</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.243580099413991</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4.917920296672051</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.318463095166805</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4.36686860117052</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4.972381548922428</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.325066057559468</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.983614604006353</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.384132268340358</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.923873191702869</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.72680063168068</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.475785345562963</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>6.123467817202262</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>4.790763233955553</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5.340168167740087</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.854590976547825</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
